--- a/data/nzd0120/nzd0120.xlsx
+++ b/data/nzd0120/nzd0120.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI245"/>
+  <dimension ref="A1:AI247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27621,6 +27621,228 @@
         <v>355.33</v>
       </c>
       <c r="AI245" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="C246" t="n">
+        <v>352.01</v>
+      </c>
+      <c r="D246" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="E246" t="n">
+        <v>347.65</v>
+      </c>
+      <c r="F246" t="n">
+        <v>344.67</v>
+      </c>
+      <c r="G246" t="n">
+        <v>343.97</v>
+      </c>
+      <c r="H246" t="n">
+        <v>349.22</v>
+      </c>
+      <c r="I246" t="n">
+        <v>354.76</v>
+      </c>
+      <c r="J246" t="n">
+        <v>361.19</v>
+      </c>
+      <c r="K246" t="n">
+        <v>364.03</v>
+      </c>
+      <c r="L246" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="M246" t="n">
+        <v>353.36</v>
+      </c>
+      <c r="N246" t="n">
+        <v>363.2</v>
+      </c>
+      <c r="O246" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="P246" t="n">
+        <v>360.96</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>357.68</v>
+      </c>
+      <c r="R246" t="n">
+        <v>358.1</v>
+      </c>
+      <c r="S246" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="T246" t="n">
+        <v>352.88</v>
+      </c>
+      <c r="U246" t="n">
+        <v>376.65</v>
+      </c>
+      <c r="V246" t="n">
+        <v>373.54</v>
+      </c>
+      <c r="W246" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="X246" t="n">
+        <v>378.11</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>384.22</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>385.45</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>375.84</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>368.63</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>357.74</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>355.49</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>357.03</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>358.68</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>370.39</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>354.7</v>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>356.77</v>
+      </c>
+      <c r="C247" t="n">
+        <v>359.72</v>
+      </c>
+      <c r="D247" t="n">
+        <v>350.36</v>
+      </c>
+      <c r="E247" t="n">
+        <v>351.54</v>
+      </c>
+      <c r="F247" t="n">
+        <v>346.33</v>
+      </c>
+      <c r="G247" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="H247" t="n">
+        <v>355.82</v>
+      </c>
+      <c r="I247" t="n">
+        <v>355.42</v>
+      </c>
+      <c r="J247" t="n">
+        <v>360.53</v>
+      </c>
+      <c r="K247" t="n">
+        <v>369.79</v>
+      </c>
+      <c r="L247" t="n">
+        <v>369.92</v>
+      </c>
+      <c r="M247" t="n">
+        <v>357.94</v>
+      </c>
+      <c r="N247" t="n">
+        <v>367.27</v>
+      </c>
+      <c r="O247" t="n">
+        <v>364.78</v>
+      </c>
+      <c r="P247" t="n">
+        <v>367.75</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>364.56</v>
+      </c>
+      <c r="R247" t="n">
+        <v>362.53</v>
+      </c>
+      <c r="S247" t="n">
+        <v>359.22</v>
+      </c>
+      <c r="T247" t="n">
+        <v>361.74</v>
+      </c>
+      <c r="U247" t="n">
+        <v>379.67</v>
+      </c>
+      <c r="V247" t="n">
+        <v>383.29</v>
+      </c>
+      <c r="W247" t="n">
+        <v>381.55</v>
+      </c>
+      <c r="X247" t="n">
+        <v>383.02</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>390.59</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>388.21</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>381.54</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>364.88</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>363.16</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>362.41</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>364.69</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>375.67</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>362.02</v>
+      </c>
+      <c r="AI247" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -27637,7 +27859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B246"/>
+  <dimension ref="A1:B248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30100,6 +30322,26 @@
       </c>
       <c r="B246" t="n">
         <v>0.99</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -30268,28 +30510,28 @@
         <v>0.0663</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1131150272350173</v>
+        <v>-0.127919081240217</v>
       </c>
       <c r="J2" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K2" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001989555737387572</v>
+        <v>0.00258318025928117</v>
       </c>
       <c r="M2" t="n">
-        <v>15.0401543920583</v>
+        <v>14.96896181174043</v>
       </c>
       <c r="N2" t="n">
-        <v>306.0971360181275</v>
+        <v>304.2010532976485</v>
       </c>
       <c r="O2" t="n">
-        <v>17.49563191251255</v>
+        <v>17.44136041992277</v>
       </c>
       <c r="P2" t="n">
-        <v>365.1124189882991</v>
+        <v>365.2828194990531</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30346,28 +30588,28 @@
         <v>0.0613</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2920714920701655</v>
+        <v>-0.2991714177794756</v>
       </c>
       <c r="J3" t="n">
+        <v>246</v>
+      </c>
+      <c r="K3" t="n">
         <v>244</v>
       </c>
-      <c r="K3" t="n">
-        <v>242</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01339061771950101</v>
+        <v>0.01427544061701413</v>
       </c>
       <c r="M3" t="n">
-        <v>14.23444283458117</v>
+        <v>14.14086288685561</v>
       </c>
       <c r="N3" t="n">
-        <v>298.2426356096186</v>
+        <v>296.0553068269448</v>
       </c>
       <c r="O3" t="n">
-        <v>17.26970282343094</v>
+        <v>17.20625778102097</v>
       </c>
       <c r="P3" t="n">
-        <v>367.6826215658123</v>
+        <v>367.7643993630671</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30424,28 +30666,28 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2968349959349367</v>
+        <v>-0.3073881908662382</v>
       </c>
       <c r="J4" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0136221175545993</v>
+        <v>0.01483834706390041</v>
       </c>
       <c r="M4" t="n">
-        <v>14.49869817242212</v>
+        <v>14.42779590544906</v>
       </c>
       <c r="N4" t="n">
-        <v>302.7673492028156</v>
+        <v>300.5764303844371</v>
       </c>
       <c r="O4" t="n">
-        <v>17.4002111827074</v>
+        <v>17.33714020201824</v>
       </c>
       <c r="P4" t="n">
-        <v>363.468137080368</v>
+        <v>363.5895683369503</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30502,28 +30744,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2577513292709794</v>
+        <v>-0.2643040057501643</v>
       </c>
       <c r="J5" t="n">
+        <v>246</v>
+      </c>
+      <c r="K5" t="n">
         <v>244</v>
       </c>
-      <c r="K5" t="n">
-        <v>242</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01137033646593688</v>
+        <v>0.01215570886700312</v>
       </c>
       <c r="M5" t="n">
-        <v>13.43261090860077</v>
+        <v>13.3491074060407</v>
       </c>
       <c r="N5" t="n">
-        <v>274.2293918022662</v>
+        <v>272.1266813274132</v>
       </c>
       <c r="O5" t="n">
-        <v>16.55987294040223</v>
+        <v>16.49626264726084</v>
       </c>
       <c r="P5" t="n">
-        <v>360.1664665140062</v>
+        <v>360.2417339419967</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30580,28 +30822,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2523769723227073</v>
+        <v>-0.2705456084076358</v>
       </c>
       <c r="J6" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K6" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01415192573955093</v>
+        <v>0.01644429381677026</v>
       </c>
       <c r="M6" t="n">
-        <v>11.75700470714612</v>
+        <v>11.73428495422867</v>
       </c>
       <c r="N6" t="n">
-        <v>212.5418928299912</v>
+        <v>211.7143849309558</v>
       </c>
       <c r="O6" t="n">
-        <v>14.57881657851526</v>
+        <v>14.55040841113939</v>
       </c>
       <c r="P6" t="n">
-        <v>362.7805657619916</v>
+        <v>362.988318810197</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30658,28 +30900,28 @@
         <v>0.0993</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3042533639351458</v>
+        <v>-0.3255332175693373</v>
       </c>
       <c r="J7" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K7" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01846378034029394</v>
+        <v>0.02133695842373673</v>
       </c>
       <c r="M7" t="n">
-        <v>12.65119313015752</v>
+        <v>12.64648240471096</v>
       </c>
       <c r="N7" t="n">
-        <v>235.7258026544456</v>
+        <v>235.0590376394275</v>
       </c>
       <c r="O7" t="n">
-        <v>15.35336453857739</v>
+        <v>15.3316351913104</v>
       </c>
       <c r="P7" t="n">
-        <v>366.0753528476801</v>
+        <v>366.3186758777553</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30736,28 +30978,28 @@
         <v>0.0776</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4037093866062511</v>
+        <v>-0.4150854293468484</v>
       </c>
       <c r="J8" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K8" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0326419192180839</v>
+        <v>0.03497150916122349</v>
       </c>
       <c r="M8" t="n">
-        <v>12.45629029618268</v>
+        <v>12.41274794732883</v>
       </c>
       <c r="N8" t="n">
-        <v>231.3661997882341</v>
+        <v>229.9251051627385</v>
       </c>
       <c r="O8" t="n">
-        <v>15.21072647141596</v>
+        <v>15.16328147739593</v>
       </c>
       <c r="P8" t="n">
-        <v>369.8193049343972</v>
+        <v>369.9493622774387</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30814,28 +31056,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4186143240870169</v>
+        <v>-0.4376415786235494</v>
       </c>
       <c r="J9" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K9" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03768349581412767</v>
+        <v>0.04156093141160555</v>
       </c>
       <c r="M9" t="n">
-        <v>11.96002617464914</v>
+        <v>11.96518938458758</v>
       </c>
       <c r="N9" t="n">
-        <v>214.3608942084764</v>
+        <v>213.6003911828991</v>
       </c>
       <c r="O9" t="n">
-        <v>14.64106875226247</v>
+        <v>14.6150741080194</v>
       </c>
       <c r="P9" t="n">
-        <v>377.2509348098734</v>
+        <v>377.4685105849686</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30892,28 +31134,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5132384706550049</v>
+        <v>-0.5309956837692444</v>
       </c>
       <c r="J10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05592048372883085</v>
+        <v>0.06039182770377616</v>
       </c>
       <c r="M10" t="n">
-        <v>11.83490205769165</v>
+        <v>11.83521568294237</v>
       </c>
       <c r="N10" t="n">
-        <v>213.0230999246205</v>
+        <v>212.1466846750559</v>
       </c>
       <c r="O10" t="n">
-        <v>14.59531088824834</v>
+        <v>14.56525607996838</v>
       </c>
       <c r="P10" t="n">
-        <v>384.7749906719735</v>
+        <v>384.9780491851473</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -30970,28 +31212,28 @@
         <v>0.0703</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7330535431022434</v>
+        <v>-0.7429421509788835</v>
       </c>
       <c r="J11" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K11" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08345760713211381</v>
+        <v>0.08683225105901615</v>
       </c>
       <c r="M11" t="n">
-        <v>13.21338668641581</v>
+        <v>13.1554541330107</v>
       </c>
       <c r="N11" t="n">
-        <v>283.7703883658916</v>
+        <v>281.7877932248422</v>
       </c>
       <c r="O11" t="n">
-        <v>16.84548569694242</v>
+        <v>16.78653606986391</v>
       </c>
       <c r="P11" t="n">
-        <v>392.013146729142</v>
+        <v>392.1259814532116</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31048,28 +31290,28 @@
         <v>0.0771</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9148580926248765</v>
+        <v>-0.9198347382093502</v>
       </c>
       <c r="J12" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K12" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1266781443757011</v>
+        <v>0.1298307902826812</v>
       </c>
       <c r="M12" t="n">
-        <v>12.70545503707388</v>
+        <v>12.62512253006125</v>
       </c>
       <c r="N12" t="n">
-        <v>277.4528278811953</v>
+        <v>275.288645405715</v>
       </c>
       <c r="O12" t="n">
-        <v>16.65691531710464</v>
+        <v>16.59182465570665</v>
       </c>
       <c r="P12" t="n">
-        <v>394.9376233459789</v>
+        <v>394.9944047458</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31126,28 +31368,28 @@
         <v>0.0861</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.724051196492246</v>
+        <v>-0.7477451482040027</v>
       </c>
       <c r="J13" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K13" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09363042790981779</v>
+        <v>0.1002512622520235</v>
       </c>
       <c r="M13" t="n">
-        <v>12.62631845254013</v>
+        <v>12.61996174723995</v>
       </c>
       <c r="N13" t="n">
-        <v>244.0258936058793</v>
+        <v>243.6022400478978</v>
       </c>
       <c r="O13" t="n">
-        <v>15.62132816395198</v>
+        <v>15.60776217296694</v>
       </c>
       <c r="P13" t="n">
-        <v>388.5840101562524</v>
+        <v>388.8544124199986</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31204,28 +31446,28 @@
         <v>0.1244</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8687153446343773</v>
+        <v>-0.8660561133830832</v>
       </c>
       <c r="J14" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K14" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1295701744021958</v>
+        <v>0.1308570749912484</v>
       </c>
       <c r="M14" t="n">
-        <v>12.80892649445026</v>
+        <v>12.72004480837008</v>
       </c>
       <c r="N14" t="n">
-        <v>243.7770165760889</v>
+        <v>241.8403304820334</v>
       </c>
       <c r="O14" t="n">
-        <v>15.61336019491285</v>
+        <v>15.55121636663941</v>
       </c>
       <c r="P14" t="n">
-        <v>386.5809770413949</v>
+        <v>386.5506088840372</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31282,28 +31524,28 @@
         <v>0.1041</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7066256170661981</v>
+        <v>-0.7065535763941385</v>
       </c>
       <c r="J15" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K15" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1448159422997918</v>
+        <v>0.1469234300082589</v>
       </c>
       <c r="M15" t="n">
-        <v>10.13772735576847</v>
+        <v>10.08072155926161</v>
       </c>
       <c r="N15" t="n">
-        <v>141.2448486776801</v>
+        <v>140.1757242994375</v>
       </c>
       <c r="O15" t="n">
-        <v>11.88464760426998</v>
+        <v>11.83958294448911</v>
       </c>
       <c r="P15" t="n">
-        <v>380.2578943584663</v>
+        <v>380.2570432402343</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31360,28 +31602,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6080193557666292</v>
+        <v>-0.6006893432799808</v>
       </c>
       <c r="J16" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K16" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1155472550942956</v>
+        <v>0.1146997029696731</v>
       </c>
       <c r="M16" t="n">
-        <v>9.905440232192026</v>
+        <v>9.855803543543951</v>
       </c>
       <c r="N16" t="n">
-        <v>136.0688964265339</v>
+        <v>135.1981798094868</v>
       </c>
       <c r="O16" t="n">
-        <v>11.66485732559699</v>
+        <v>11.62747521216394</v>
       </c>
       <c r="P16" t="n">
-        <v>376.1044485769179</v>
+        <v>376.0207602400641</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31438,28 +31680,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5950176594437356</v>
+        <v>-0.5892372770004844</v>
       </c>
       <c r="J17" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K17" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09231409038585892</v>
+        <v>0.0920656806581196</v>
       </c>
       <c r="M17" t="n">
-        <v>10.81417199520496</v>
+        <v>10.75421158476282</v>
       </c>
       <c r="N17" t="n">
-        <v>166.7546488430768</v>
+        <v>165.5856690594928</v>
       </c>
       <c r="O17" t="n">
-        <v>12.91335157281319</v>
+        <v>12.86800952204702</v>
       </c>
       <c r="P17" t="n">
-        <v>373.4273888276488</v>
+        <v>373.361259386481</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31516,28 +31758,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6189218403894817</v>
+        <v>-0.6077479136325024</v>
       </c>
       <c r="J18" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K18" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0935852035151622</v>
+        <v>0.0918276329226817</v>
       </c>
       <c r="M18" t="n">
-        <v>11.04676692465972</v>
+        <v>11.00917744865644</v>
       </c>
       <c r="N18" t="n">
-        <v>177.7223529298859</v>
+        <v>176.655637985567</v>
       </c>
       <c r="O18" t="n">
-        <v>13.33125473951668</v>
+        <v>13.2911864777215</v>
       </c>
       <c r="P18" t="n">
-        <v>370.0964492446071</v>
+        <v>369.9686547661929</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31594,28 +31836,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.596618728322836</v>
+        <v>-0.5919345396104148</v>
       </c>
       <c r="J19" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K19" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1065557148727033</v>
+        <v>0.1066868716671447</v>
       </c>
       <c r="M19" t="n">
-        <v>10.47230903370443</v>
+        <v>10.40892733871684</v>
       </c>
       <c r="N19" t="n">
-        <v>142.9667790469598</v>
+        <v>141.8814947086656</v>
       </c>
       <c r="O19" t="n">
-        <v>11.95687162459143</v>
+        <v>11.91140187839641</v>
       </c>
       <c r="P19" t="n">
-        <v>370.7386457866991</v>
+        <v>370.685068686331</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31672,28 +31914,28 @@
         <v>0.0849</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3725174965173085</v>
+        <v>-0.3778894237110099</v>
       </c>
       <c r="J20" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K20" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0430959654413331</v>
+        <v>0.04497848472866495</v>
       </c>
       <c r="M20" t="n">
-        <v>10.25982656347196</v>
+        <v>10.21247823289283</v>
       </c>
       <c r="N20" t="n">
-        <v>148.1610933772032</v>
+        <v>147.1907380534245</v>
       </c>
       <c r="O20" t="n">
-        <v>12.17214415693485</v>
+        <v>12.13221900780828</v>
       </c>
       <c r="P20" t="n">
-        <v>370.273422079181</v>
+        <v>370.3346936917364</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31750,28 +31992,28 @@
         <v>0.1177</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.587134193675256</v>
+        <v>-0.5603567339715557</v>
       </c>
       <c r="J21" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K21" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08145611764313831</v>
+        <v>0.07523201390148371</v>
       </c>
       <c r="M21" t="n">
-        <v>11.41877719146906</v>
+        <v>11.45601533910036</v>
       </c>
       <c r="N21" t="n">
-        <v>186.2093954151031</v>
+        <v>186.6572852331569</v>
       </c>
       <c r="O21" t="n">
-        <v>13.64585634597928</v>
+        <v>13.66225769165393</v>
       </c>
       <c r="P21" t="n">
-        <v>377.9727813325287</v>
+        <v>377.6665649209558</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -31828,28 +32070,28 @@
         <v>0.07729999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7445834092742388</v>
+        <v>-0.7188454757780013</v>
       </c>
       <c r="J22" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K22" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1260881483927709</v>
+        <v>0.1192701276302223</v>
       </c>
       <c r="M22" t="n">
-        <v>11.47836082195658</v>
+        <v>11.50274227971963</v>
       </c>
       <c r="N22" t="n">
-        <v>181.6678701286908</v>
+        <v>182.139949166769</v>
       </c>
       <c r="O22" t="n">
-        <v>13.47842239020171</v>
+        <v>13.49592342771583</v>
       </c>
       <c r="P22" t="n">
-        <v>383.1638825621403</v>
+        <v>382.8671398435663</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -31906,28 +32148,28 @@
         <v>0.0822</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9090904258909341</v>
+        <v>-0.8783544202577931</v>
       </c>
       <c r="J23" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K23" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1632305848984515</v>
+        <v>0.1546416129219721</v>
       </c>
       <c r="M23" t="n">
-        <v>11.96963914221159</v>
+        <v>12.01324209714203</v>
       </c>
       <c r="N23" t="n">
-        <v>202.9406605441102</v>
+        <v>203.9575247725413</v>
       </c>
       <c r="O23" t="n">
-        <v>14.24572428990924</v>
+        <v>14.28136984930162</v>
       </c>
       <c r="P23" t="n">
-        <v>383.9164447357899</v>
+        <v>383.5649433918916</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -31984,28 +32226,28 @@
         <v>0.1105</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8525288787178235</v>
+        <v>-0.8290820171542416</v>
       </c>
       <c r="J24" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K24" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1623402865950688</v>
+        <v>0.1560906853081783</v>
       </c>
       <c r="M24" t="n">
-        <v>11.20582680331548</v>
+        <v>11.20960406987295</v>
       </c>
       <c r="N24" t="n">
-        <v>179.6429423467288</v>
+        <v>179.7212535587452</v>
       </c>
       <c r="O24" t="n">
-        <v>13.40309450637161</v>
+        <v>13.4060155735679</v>
       </c>
       <c r="P24" t="n">
-        <v>389.3277101263635</v>
+        <v>389.0595711786999</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -32062,28 +32304,28 @@
         <v>0.0989</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8276605027385061</v>
+        <v>-0.8080035305994343</v>
       </c>
       <c r="J25" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K25" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L25" t="n">
-        <v>0.186654601944316</v>
+        <v>0.180906634368132</v>
       </c>
       <c r="M25" t="n">
-        <v>9.917586897614628</v>
+        <v>9.909227305987541</v>
       </c>
       <c r="N25" t="n">
-        <v>142.9853074098723</v>
+        <v>142.952280017597</v>
       </c>
       <c r="O25" t="n">
-        <v>11.95764639926571</v>
+        <v>11.9562653039148</v>
       </c>
       <c r="P25" t="n">
-        <v>397.7280389215669</v>
+        <v>397.5032313932884</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -32140,28 +32382,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6658781706388991</v>
+        <v>-0.650523099671436</v>
       </c>
       <c r="J26" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K26" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1468409945459934</v>
+        <v>0.1426143312448593</v>
       </c>
       <c r="M26" t="n">
-        <v>9.388277842107199</v>
+        <v>9.377288450538725</v>
       </c>
       <c r="N26" t="n">
-        <v>121.5519947827601</v>
+        <v>121.2003391189927</v>
       </c>
       <c r="O26" t="n">
-        <v>11.02506212149211</v>
+        <v>11.00910255738371</v>
       </c>
       <c r="P26" t="n">
-        <v>395.5192953815806</v>
+        <v>395.342104788224</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -32218,28 +32460,28 @@
         <v>0.0572</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5953388586050125</v>
+        <v>-0.590608680085035</v>
       </c>
       <c r="J27" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K27" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1113221845051321</v>
+        <v>0.111411871793147</v>
       </c>
       <c r="M27" t="n">
-        <v>9.816340875057747</v>
+        <v>9.760703691765318</v>
       </c>
       <c r="N27" t="n">
-        <v>133.4999037867127</v>
+        <v>132.5360509376522</v>
       </c>
       <c r="O27" t="n">
-        <v>11.55421584473445</v>
+        <v>11.5124302793829</v>
       </c>
       <c r="P27" t="n">
-        <v>391.6554238419249</v>
+        <v>391.6008182113925</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -32296,28 +32538,28 @@
         <v>0.0688</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5704044451503956</v>
+        <v>-0.5651796373842379</v>
       </c>
       <c r="J28" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K28" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1021930642838608</v>
+        <v>0.1020665863879328</v>
       </c>
       <c r="M28" t="n">
-        <v>10.16446801953956</v>
+        <v>10.10827817264624</v>
       </c>
       <c r="N28" t="n">
-        <v>134.8705752535032</v>
+        <v>133.8748184511448</v>
       </c>
       <c r="O28" t="n">
-        <v>11.61337914878797</v>
+        <v>11.57042862002721</v>
       </c>
       <c r="P28" t="n">
-        <v>382.6550051933637</v>
+        <v>382.5946996804051</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -32374,28 +32616,28 @@
         <v>0.0863</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7788568868852211</v>
+        <v>-0.7746297012350387</v>
       </c>
       <c r="J29" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K29" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2088924798012197</v>
+        <v>0.2098053827921186</v>
       </c>
       <c r="M29" t="n">
-        <v>8.753595865291624</v>
+        <v>8.711691987575502</v>
       </c>
       <c r="N29" t="n">
-        <v>108.3971613261609</v>
+        <v>107.664138541025</v>
       </c>
       <c r="O29" t="n">
-        <v>10.41139574342273</v>
+        <v>10.37613312082228</v>
       </c>
       <c r="P29" t="n">
-        <v>379.4024653019622</v>
+        <v>379.3536572087008</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -32452,28 +32694,28 @@
         <v>0.0877</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7729260441470501</v>
+        <v>-0.7760445042586255</v>
       </c>
       <c r="J30" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K30" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2261197181010771</v>
+        <v>0.2304061350240991</v>
       </c>
       <c r="M30" t="n">
-        <v>8.347535402868449</v>
+        <v>8.309538009286548</v>
       </c>
       <c r="N30" t="n">
-        <v>96.47195985425893</v>
+        <v>95.83102930283125</v>
       </c>
       <c r="O30" t="n">
-        <v>9.822014042662479</v>
+        <v>9.789332423757569</v>
       </c>
       <c r="P30" t="n">
-        <v>381.5055311692815</v>
+        <v>381.5414802884038</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -32530,28 +32772,28 @@
         <v>0.1087</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6799745024707056</v>
+        <v>-0.6839189462935739</v>
       </c>
       <c r="J31" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K31" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1882723442736287</v>
+        <v>0.1926356348509101</v>
       </c>
       <c r="M31" t="n">
-        <v>8.31439640851567</v>
+        <v>8.267810009140829</v>
       </c>
       <c r="N31" t="n">
-        <v>94.05869334870727</v>
+        <v>93.39154448130326</v>
       </c>
       <c r="O31" t="n">
-        <v>9.698386120829964</v>
+        <v>9.66393007431776</v>
       </c>
       <c r="P31" t="n">
-        <v>379.9259370860284</v>
+        <v>379.9714271879137</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -32608,28 +32850,28 @@
         <v>0.1004</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4132734850957624</v>
+        <v>-0.4386785130588333</v>
       </c>
       <c r="J32" t="n">
+        <v>246</v>
+      </c>
+      <c r="K32" t="n">
         <v>244</v>
       </c>
-      <c r="K32" t="n">
-        <v>242</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.07866482497825089</v>
+        <v>0.08768159300251832</v>
       </c>
       <c r="M32" t="n">
-        <v>8.258661014417301</v>
+        <v>8.328706792148054</v>
       </c>
       <c r="N32" t="n">
-        <v>93.46145681135501</v>
+        <v>94.45834086017291</v>
       </c>
       <c r="O32" t="n">
-        <v>9.667546576632306</v>
+        <v>9.718968096468519</v>
       </c>
       <c r="P32" t="n">
-        <v>387.1229920657123</v>
+        <v>387.4179815300898</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -32686,28 +32928,28 @@
         <v>0.1039</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3501116720060308</v>
+        <v>-0.3741531702142162</v>
       </c>
       <c r="J33" t="n">
+        <v>246</v>
+      </c>
+      <c r="K33" t="n">
         <v>244</v>
       </c>
-      <c r="K33" t="n">
-        <v>242</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.06944947725643136</v>
+        <v>0.07835660324006055</v>
       </c>
       <c r="M33" t="n">
-        <v>7.24093765571633</v>
+        <v>7.291982381293765</v>
       </c>
       <c r="N33" t="n">
-        <v>76.7369519840702</v>
+        <v>77.67759223399653</v>
       </c>
       <c r="O33" t="n">
-        <v>8.75996301271131</v>
+        <v>8.813489220166808</v>
       </c>
       <c r="P33" t="n">
-        <v>396.0173083913759</v>
+        <v>396.2964670929476</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -32764,28 +33006,28 @@
         <v>0.0945</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5078975555732737</v>
+        <v>-0.529355445217121</v>
       </c>
       <c r="J34" t="n">
+        <v>246</v>
+      </c>
+      <c r="K34" t="n">
         <v>244</v>
       </c>
-      <c r="K34" t="n">
-        <v>242</v>
-      </c>
       <c r="L34" t="n">
-        <v>0.1415588532265859</v>
+        <v>0.1519040738058871</v>
       </c>
       <c r="M34" t="n">
-        <v>7.119356149694569</v>
+        <v>7.149394489558995</v>
       </c>
       <c r="N34" t="n">
-        <v>73.08800796735646</v>
+        <v>73.80400123194693</v>
       </c>
       <c r="O34" t="n">
-        <v>8.54915247070471</v>
+        <v>8.590925516610357</v>
       </c>
       <c r="P34" t="n">
-        <v>384.0340752959658</v>
+        <v>384.2832226946836</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -32823,7 +33065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI245"/>
+  <dimension ref="A1:AI247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76059,6 +76301,360 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>-36.2335276802118,175.47718015772813</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>-36.234252052121825,175.4771964084765</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>-36.23497711950279,175.47716050600044</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-36.23570186576438,175.47714795540145</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-36.23643066212434,175.47711472616118</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-36.23716161230296,175.47715230284268</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-36.23788084751648,175.4773020008099</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-36.23859574089055,175.4774545979882</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-36.23930968036739,175.4776170258223</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>-36.2400267097073,175.4777394259904</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-36.24073515755737,175.4779060106412</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>-36.24146726624757,175.47797020272637</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>-36.24215240312881,175.47827666836162</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>-36.24286867350583,175.47842673266018</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>-36.24356979755629,175.4786528380543</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>-36.244283130520856,175.47881759133935</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>-36.244988499953074,175.4790223099326</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>-36.24569868037725,175.47920283281726</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>-36.246412252462754,175.47936628854674</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>-36.24706131555765,175.4798208952307</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>-36.24774134998465,175.48006006928009</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>-36.24838192783383,175.48045872867146</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>-36.24901444066061,175.48089027447057</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>-36.249609765459034,175.48136126833234</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>-36.25017449119171,175.48189396880835</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>-36.250810332717045,175.48234144561297</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>-36.25143307517831,175.48281016707725</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>-36.252076304143856,175.4832466401521</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>-36.252660791595495,175.4837844217543</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>-36.25314416284301,175.48446002093408</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>-36.25362486600889,175.4851342131221</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>-36.25393608574909,175.48590589122892</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>-36.254225514279575,175.48672900775412</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:05:46+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>-36.23352674896146,175.47724932381004</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>-36.234250897749504,175.477282144072</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>-36.23497688294426,175.47717807584476</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-36.23570128333933,175.47719121320227</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-36.236430038125846,175.47713317243492</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-36.237158878187245,175.47718862654776</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-36.23787382404021,175.4773748928878</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-36.238595038535685,175.47746188726123</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-36.239310382731645,175.4776097364848</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>-36.24001896907198,175.47780277442666</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-36.240727568894016,175.47794973074585</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>-36.24145741681283,175.4780196719509</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>-36.242143650369805,175.47832062935262</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>-36.24285529698578,175.4784939168728</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>-36.24355519509925,175.4787261796308</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>-36.24426833443429,175.47889190568847</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>-36.24497897276185,175.47907016100518</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>-36.24569235755637,175.4792345897857</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>-36.246393197852434,175.4794619923353</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>-36.24705361331779,175.47985311397494</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>-36.24770691776399,175.4801598453575</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>-36.24835223791395,175.48053056331415</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>-36.24899363230163,175.48093847277406</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>-36.249578353590174,175.48142057206104</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>-36.25015943188191,175.4819184008547</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>-36.25077923184986,175.48239190337173</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>-36.251411195361754,175.48284566474393</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>-36.252036543767424,175.48330907976077</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>-36.252613065979126,175.48384612956576</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>-36.25310798953448,175.484499860442</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>-36.25358218548586,175.4851753592967</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>-36.25389217049015,175.4859284768257</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>-36.254160862055606,175.48674510254517</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0120/nzd0120.xlsx
+++ b/data/nzd0120/nzd0120.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI247"/>
+  <dimension ref="A1:AI249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27845,6 +27845,228 @@
       <c r="AI247" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>360.3</v>
+      </c>
+      <c r="C248" t="n">
+        <v>363.82</v>
+      </c>
+      <c r="D248" t="n">
+        <v>356.6</v>
+      </c>
+      <c r="E248" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="F248" t="n">
+        <v>352.23</v>
+      </c>
+      <c r="G248" t="n">
+        <v>356.5</v>
+      </c>
+      <c r="H248" t="n">
+        <v>361.24</v>
+      </c>
+      <c r="I248" t="n">
+        <v>362.97</v>
+      </c>
+      <c r="J248" t="n">
+        <v>367.89</v>
+      </c>
+      <c r="K248" t="n">
+        <v>374.14</v>
+      </c>
+      <c r="L248" t="n">
+        <v>376.68</v>
+      </c>
+      <c r="M248" t="n">
+        <v>371.72</v>
+      </c>
+      <c r="N248" t="n">
+        <v>374.81</v>
+      </c>
+      <c r="O248" t="n">
+        <v>374.04</v>
+      </c>
+      <c r="P248" t="n">
+        <v>372.75</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>374.42</v>
+      </c>
+      <c r="R248" t="n">
+        <v>374.29</v>
+      </c>
+      <c r="S248" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="T248" t="n">
+        <v>377.92</v>
+      </c>
+      <c r="U248" t="n">
+        <v>387.17</v>
+      </c>
+      <c r="V248" t="n">
+        <v>387.65</v>
+      </c>
+      <c r="W248" t="n">
+        <v>389.28</v>
+      </c>
+      <c r="X248" t="n">
+        <v>391.97</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>396.33</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>386.9</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>374.75</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>373.46</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>370.76</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>380.89</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>387.85</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>359.61</v>
+      </c>
+      <c r="C249" t="n">
+        <v>361.16</v>
+      </c>
+      <c r="D249" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="E249" t="n">
+        <v>357.08</v>
+      </c>
+      <c r="F249" t="n">
+        <v>352.76</v>
+      </c>
+      <c r="G249" t="n">
+        <v>356.93</v>
+      </c>
+      <c r="H249" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="I249" t="n">
+        <v>361.68</v>
+      </c>
+      <c r="J249" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="K249" t="n">
+        <v>373.05</v>
+      </c>
+      <c r="L249" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="M249" t="n">
+        <v>368.89</v>
+      </c>
+      <c r="N249" t="n">
+        <v>370.53</v>
+      </c>
+      <c r="O249" t="n">
+        <v>368.71</v>
+      </c>
+      <c r="P249" t="n">
+        <v>365.76</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>369.84</v>
+      </c>
+      <c r="R249" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="S249" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="T249" t="n">
+        <v>372.28</v>
+      </c>
+      <c r="U249" t="n">
+        <v>382.71</v>
+      </c>
+      <c r="V249" t="n">
+        <v>383.22</v>
+      </c>
+      <c r="W249" t="n">
+        <v>386.9</v>
+      </c>
+      <c r="X249" t="n">
+        <v>391.97</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>396.33</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>386.9</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>374.75</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>373.46</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>370.76</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>380.89</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>387.85</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -27859,7 +28081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B248"/>
+  <dimension ref="A1:B250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30342,6 +30564,26 @@
       </c>
       <c r="B248" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>-0.59</v>
       </c>
     </row>
   </sheetData>
@@ -30510,28 +30752,28 @@
         <v>0.0663</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.127919081240217</v>
+        <v>-0.1312751063596569</v>
       </c>
       <c r="J2" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K2" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00258318025928117</v>
+        <v>0.002768328975716994</v>
       </c>
       <c r="M2" t="n">
-        <v>14.96896181174043</v>
+        <v>14.85718293667566</v>
       </c>
       <c r="N2" t="n">
-        <v>304.2010532976485</v>
+        <v>301.7080983622513</v>
       </c>
       <c r="O2" t="n">
-        <v>17.44136041992277</v>
+        <v>17.3697466407041</v>
       </c>
       <c r="P2" t="n">
-        <v>365.2828194990531</v>
+        <v>365.3216572733813</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30588,28 +30830,28 @@
         <v>0.0613</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2991714177794756</v>
+        <v>-0.2946708012897212</v>
       </c>
       <c r="J3" t="n">
+        <v>248</v>
+      </c>
+      <c r="K3" t="n">
         <v>246</v>
       </c>
-      <c r="K3" t="n">
-        <v>244</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01427544061701413</v>
+        <v>0.01409342030369953</v>
       </c>
       <c r="M3" t="n">
-        <v>14.14086288685561</v>
+        <v>14.05357270861096</v>
       </c>
       <c r="N3" t="n">
-        <v>296.0553068269448</v>
+        <v>293.7180352265968</v>
       </c>
       <c r="O3" t="n">
-        <v>17.20625778102097</v>
+        <v>17.13820396735308</v>
       </c>
       <c r="P3" t="n">
-        <v>367.7643993630671</v>
+        <v>367.712333102666</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30666,28 +30908,28 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3073881908662382</v>
+        <v>-0.3069365514573178</v>
       </c>
       <c r="J4" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K4" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01483834706390041</v>
+        <v>0.0150552883015852</v>
       </c>
       <c r="M4" t="n">
-        <v>14.42779590544906</v>
+        <v>14.31715462918932</v>
       </c>
       <c r="N4" t="n">
-        <v>300.5764303844371</v>
+        <v>298.1294376533864</v>
       </c>
       <c r="O4" t="n">
-        <v>17.33714020201824</v>
+        <v>17.26642515558407</v>
       </c>
       <c r="P4" t="n">
-        <v>363.5895683369503</v>
+        <v>363.5843765385849</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30744,28 +30986,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2643040057501643</v>
+        <v>-0.2564767591734949</v>
       </c>
       <c r="J5" t="n">
+        <v>248</v>
+      </c>
+      <c r="K5" t="n">
         <v>246</v>
       </c>
-      <c r="K5" t="n">
-        <v>244</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.01215570886700312</v>
+        <v>0.01164966251045696</v>
       </c>
       <c r="M5" t="n">
-        <v>13.3491074060407</v>
+        <v>13.2820220532156</v>
       </c>
       <c r="N5" t="n">
-        <v>272.1266813274132</v>
+        <v>270.0846396832442</v>
       </c>
       <c r="O5" t="n">
-        <v>16.49626264726084</v>
+        <v>16.43425202688714</v>
       </c>
       <c r="P5" t="n">
-        <v>360.2417339419967</v>
+        <v>360.1513971510988</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30822,28 +31064,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2705456084076358</v>
+        <v>-0.2761543756578764</v>
       </c>
       <c r="J6" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K6" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01644429381677026</v>
+        <v>0.01741130817684733</v>
       </c>
       <c r="M6" t="n">
-        <v>11.73428495422867</v>
+        <v>11.66183866899529</v>
       </c>
       <c r="N6" t="n">
-        <v>211.7143849309558</v>
+        <v>210.0946566112819</v>
       </c>
       <c r="O6" t="n">
-        <v>14.55040841113939</v>
+        <v>14.49464234161305</v>
       </c>
       <c r="P6" t="n">
-        <v>362.988318810197</v>
+        <v>363.0527583810164</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30900,28 +31142,28 @@
         <v>0.0993</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3255332175693373</v>
+        <v>-0.3271904352192705</v>
       </c>
       <c r="J7" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K7" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02133695842373673</v>
+        <v>0.02192150355132427</v>
       </c>
       <c r="M7" t="n">
-        <v>12.64648240471096</v>
+        <v>12.55202607523866</v>
       </c>
       <c r="N7" t="n">
-        <v>235.0590376394275</v>
+        <v>233.1714434891171</v>
       </c>
       <c r="O7" t="n">
-        <v>15.3316351913104</v>
+        <v>15.26995230801711</v>
       </c>
       <c r="P7" t="n">
-        <v>366.3186758777553</v>
+        <v>366.3377105608581</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -30978,28 +31220,28 @@
         <v>0.0776</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4150854293468484</v>
+        <v>-0.4121096896178313</v>
       </c>
       <c r="J8" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K8" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03497150916122349</v>
+        <v>0.03507282001265966</v>
       </c>
       <c r="M8" t="n">
-        <v>12.41274794732883</v>
+        <v>12.32552234734423</v>
       </c>
       <c r="N8" t="n">
-        <v>229.9251051627385</v>
+        <v>228.097378921032</v>
       </c>
       <c r="O8" t="n">
-        <v>15.16328147739593</v>
+        <v>15.10289306460957</v>
       </c>
       <c r="P8" t="n">
-        <v>369.9493622774387</v>
+        <v>369.9151858092152</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31056,28 +31298,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4376415786235494</v>
+        <v>-0.4436404396187437</v>
       </c>
       <c r="J9" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K9" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04156093141160555</v>
+        <v>0.04335969956487695</v>
       </c>
       <c r="M9" t="n">
-        <v>11.96518938458758</v>
+        <v>11.90034889587331</v>
       </c>
       <c r="N9" t="n">
-        <v>213.6003911828991</v>
+        <v>211.9802753254733</v>
       </c>
       <c r="O9" t="n">
-        <v>14.6150741080194</v>
+        <v>14.55954241470086</v>
       </c>
       <c r="P9" t="n">
-        <v>377.4685105849686</v>
+        <v>377.5374637197315</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31134,28 +31376,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5309956837692444</v>
+        <v>-0.5367918479599988</v>
       </c>
       <c r="J10" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K10" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06039182770377616</v>
+        <v>0.06262968198735719</v>
       </c>
       <c r="M10" t="n">
-        <v>11.83521568294237</v>
+        <v>11.77086430992744</v>
       </c>
       <c r="N10" t="n">
-        <v>212.1466846750559</v>
+        <v>210.5298127682835</v>
       </c>
       <c r="O10" t="n">
-        <v>14.56525607996838</v>
+        <v>14.50964550801581</v>
       </c>
       <c r="P10" t="n">
-        <v>384.9780491851473</v>
+        <v>385.0446649587525</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31212,28 +31454,28 @@
         <v>0.0703</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7429421509788835</v>
+        <v>-0.7410204820560077</v>
       </c>
       <c r="J11" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K11" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08683225105901615</v>
+        <v>0.08781311104258505</v>
       </c>
       <c r="M11" t="n">
-        <v>13.1554541330107</v>
+        <v>13.05740363631243</v>
       </c>
       <c r="N11" t="n">
-        <v>281.7877932248422</v>
+        <v>279.5184953212283</v>
       </c>
       <c r="O11" t="n">
-        <v>16.78653606986391</v>
+        <v>16.71880663567913</v>
       </c>
       <c r="P11" t="n">
-        <v>392.1259814532116</v>
+        <v>392.1039596748012</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31290,28 +31532,28 @@
         <v>0.0771</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9198347382093502</v>
+        <v>-0.9095053275743888</v>
       </c>
       <c r="J12" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K12" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1298307902826812</v>
+        <v>0.1291390309410927</v>
       </c>
       <c r="M12" t="n">
-        <v>12.62512253006125</v>
+        <v>12.57205537433814</v>
       </c>
       <c r="N12" t="n">
-        <v>275.288645405715</v>
+        <v>273.3552764390033</v>
       </c>
       <c r="O12" t="n">
-        <v>16.59182465570665</v>
+        <v>16.53345930043085</v>
       </c>
       <c r="P12" t="n">
-        <v>394.9944047458</v>
+        <v>394.8759333479719</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31368,28 +31610,28 @@
         <v>0.0861</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7477451482040027</v>
+        <v>-0.745646230254745</v>
       </c>
       <c r="J13" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K13" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1002512622520235</v>
+        <v>0.1013201917717891</v>
       </c>
       <c r="M13" t="n">
-        <v>12.61996174723995</v>
+        <v>12.53038931228133</v>
       </c>
       <c r="N13" t="n">
-        <v>243.6022400478978</v>
+        <v>241.6575105177559</v>
       </c>
       <c r="O13" t="n">
-        <v>15.60776217296694</v>
+        <v>15.54533725969803</v>
       </c>
       <c r="P13" t="n">
-        <v>388.8544124199986</v>
+        <v>388.8303879879056</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31446,28 +31688,28 @@
         <v>0.1244</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8660561133830832</v>
+        <v>-0.8507926568769789</v>
       </c>
       <c r="J14" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K14" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1308570749912484</v>
+        <v>0.1285014100764571</v>
       </c>
       <c r="M14" t="n">
-        <v>12.72004480837008</v>
+        <v>12.68271006963552</v>
       </c>
       <c r="N14" t="n">
-        <v>241.8403304820334</v>
+        <v>240.5647134869037</v>
       </c>
       <c r="O14" t="n">
-        <v>15.55121636663941</v>
+        <v>15.51014872549273</v>
       </c>
       <c r="P14" t="n">
-        <v>386.5506088840372</v>
+        <v>386.3756261268562</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31524,28 +31766,28 @@
         <v>0.1041</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7065535763941385</v>
+        <v>-0.6900037946122598</v>
       </c>
       <c r="J15" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K15" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1469234300082589</v>
+        <v>0.1424997105934247</v>
       </c>
       <c r="M15" t="n">
-        <v>10.08072155926161</v>
+        <v>10.08746779435898</v>
       </c>
       <c r="N15" t="n">
-        <v>140.1757242994375</v>
+        <v>139.8601665258326</v>
       </c>
       <c r="O15" t="n">
-        <v>11.83958294448911</v>
+        <v>11.82624904717606</v>
       </c>
       <c r="P15" t="n">
-        <v>380.2570432402343</v>
+        <v>380.0669644924277</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31602,28 +31844,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6006893432799808</v>
+        <v>-0.5852847886978173</v>
       </c>
       <c r="J16" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K16" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1146997029696731</v>
+        <v>0.1106944501843604</v>
       </c>
       <c r="M16" t="n">
-        <v>9.855803543543951</v>
+        <v>9.840441506629348</v>
       </c>
       <c r="N16" t="n">
-        <v>135.1981798094868</v>
+        <v>134.8606636893585</v>
       </c>
       <c r="O16" t="n">
-        <v>11.62747521216394</v>
+        <v>11.61295241053534</v>
       </c>
       <c r="P16" t="n">
-        <v>376.0207602400641</v>
+        <v>375.844206754321</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31680,28 +31922,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5892372770004844</v>
+        <v>-0.5650168398035013</v>
       </c>
       <c r="J17" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K17" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0920656806581196</v>
+        <v>0.08586500499703353</v>
       </c>
       <c r="M17" t="n">
-        <v>10.75421158476282</v>
+        <v>10.78036944482125</v>
       </c>
       <c r="N17" t="n">
-        <v>165.5856690594928</v>
+        <v>165.9157859929904</v>
       </c>
       <c r="O17" t="n">
-        <v>12.86800952204702</v>
+        <v>12.88083017483696</v>
       </c>
       <c r="P17" t="n">
-        <v>373.361259386481</v>
+        <v>373.083026160236</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31758,28 +32000,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6077479136325024</v>
+        <v>-0.5734747028874323</v>
       </c>
       <c r="J18" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K18" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0918276329226817</v>
+        <v>0.08252878902102567</v>
       </c>
       <c r="M18" t="n">
-        <v>11.00917744865644</v>
+        <v>11.07865551132486</v>
       </c>
       <c r="N18" t="n">
-        <v>176.655637985567</v>
+        <v>178.4786584744382</v>
       </c>
       <c r="O18" t="n">
-        <v>13.2911864777215</v>
+        <v>13.35959050549223</v>
       </c>
       <c r="P18" t="n">
-        <v>369.9686547661929</v>
+        <v>369.5748310861912</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -31836,28 +32078,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5919345396104148</v>
+        <v>-0.5709253572817011</v>
       </c>
       <c r="J19" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K19" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1066868716671447</v>
+        <v>0.100792819396832</v>
       </c>
       <c r="M19" t="n">
-        <v>10.40892733871684</v>
+        <v>10.42294312250323</v>
       </c>
       <c r="N19" t="n">
-        <v>141.8814947086656</v>
+        <v>141.9579199736391</v>
       </c>
       <c r="O19" t="n">
-        <v>11.91140187839641</v>
+        <v>11.91460951830311</v>
       </c>
       <c r="P19" t="n">
-        <v>370.685068686331</v>
+        <v>370.4436476913031</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -31914,28 +32156,28 @@
         <v>0.0849</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3778894237110099</v>
+        <v>-0.3529741643035026</v>
       </c>
       <c r="J20" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K20" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04497848472866495</v>
+        <v>0.03967334835602698</v>
       </c>
       <c r="M20" t="n">
-        <v>10.21247823289283</v>
+        <v>10.24798567247942</v>
       </c>
       <c r="N20" t="n">
-        <v>147.1907380534245</v>
+        <v>147.7854324696974</v>
       </c>
       <c r="O20" t="n">
-        <v>12.13221900780828</v>
+        <v>12.15670319082018</v>
       </c>
       <c r="P20" t="n">
-        <v>370.3346936917364</v>
+        <v>370.0490393011399</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -31992,28 +32234,28 @@
         <v>0.1177</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5603567339715557</v>
+        <v>-0.523088346297637</v>
       </c>
       <c r="J21" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K21" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07523201390148371</v>
+        <v>0.06599758017237567</v>
       </c>
       <c r="M21" t="n">
-        <v>11.45601533910036</v>
+        <v>11.5452709967642</v>
       </c>
       <c r="N21" t="n">
-        <v>186.6572852331569</v>
+        <v>189.0344109200172</v>
       </c>
       <c r="O21" t="n">
-        <v>13.66225769165393</v>
+        <v>13.74897854096868</v>
       </c>
       <c r="P21" t="n">
-        <v>377.6665649209558</v>
+        <v>377.2383984107556</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32070,28 +32312,28 @@
         <v>0.07729999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7188454757780013</v>
+        <v>-0.6820196269420797</v>
       </c>
       <c r="J22" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K22" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1192701276302223</v>
+        <v>0.1083873551199093</v>
       </c>
       <c r="M22" t="n">
-        <v>11.50274227971963</v>
+        <v>11.58670992514755</v>
       </c>
       <c r="N22" t="n">
-        <v>182.139949166769</v>
+        <v>184.3864888012958</v>
       </c>
       <c r="O22" t="n">
-        <v>13.49592342771583</v>
+        <v>13.57889865936468</v>
       </c>
       <c r="P22" t="n">
-        <v>382.8671398435663</v>
+        <v>382.4406515301198</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32148,28 +32390,28 @@
         <v>0.0822</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8783544202577931</v>
+        <v>-0.8315123537854106</v>
       </c>
       <c r="J23" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K23" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1546416129219721</v>
+        <v>0.1393906080444529</v>
       </c>
       <c r="M23" t="n">
-        <v>12.01324209714203</v>
+        <v>12.12684907923363</v>
       </c>
       <c r="N23" t="n">
-        <v>203.9575247725413</v>
+        <v>208.3918693219768</v>
       </c>
       <c r="O23" t="n">
-        <v>14.28136984930162</v>
+        <v>14.43578433345334</v>
       </c>
       <c r="P23" t="n">
-        <v>383.5649433918916</v>
+        <v>383.0267315959823</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32226,28 +32468,28 @@
         <v>0.1105</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8290820171542416</v>
+        <v>-0.7871546833880105</v>
       </c>
       <c r="J24" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K24" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1560906853081783</v>
+        <v>0.1417549718793611</v>
       </c>
       <c r="M24" t="n">
-        <v>11.20960406987295</v>
+        <v>11.28799187152317</v>
       </c>
       <c r="N24" t="n">
-        <v>179.7212535587452</v>
+        <v>183.1318798004872</v>
       </c>
       <c r="O24" t="n">
-        <v>13.4060155735679</v>
+        <v>13.53262279827851</v>
       </c>
       <c r="P24" t="n">
-        <v>389.0595711786999</v>
+        <v>388.5777922687729</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -32304,28 +32546,28 @@
         <v>0.0989</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8080035305994343</v>
+        <v>-0.764179509930236</v>
       </c>
       <c r="J25" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K25" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L25" t="n">
-        <v>0.180906634368132</v>
+        <v>0.1623288234131177</v>
       </c>
       <c r="M25" t="n">
-        <v>9.909227305987541</v>
+        <v>9.994071898206808</v>
       </c>
       <c r="N25" t="n">
-        <v>142.952280017597</v>
+        <v>147.1090864345057</v>
       </c>
       <c r="O25" t="n">
-        <v>11.9562653039148</v>
+        <v>12.12885346743482</v>
       </c>
       <c r="P25" t="n">
-        <v>397.5032313932884</v>
+        <v>396.9996581086074</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -32382,28 +32624,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.650523099671436</v>
+        <v>-0.619409358320572</v>
       </c>
       <c r="J26" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K26" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1426143312448593</v>
+        <v>0.1305982517659046</v>
       </c>
       <c r="M26" t="n">
-        <v>9.377288450538725</v>
+        <v>9.435862059060746</v>
       </c>
       <c r="N26" t="n">
-        <v>121.2003391189927</v>
+        <v>122.8369104227538</v>
       </c>
       <c r="O26" t="n">
-        <v>11.00910255738371</v>
+        <v>11.0831814215393</v>
       </c>
       <c r="P26" t="n">
-        <v>395.342104788224</v>
+        <v>394.9813633300875</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -32460,28 +32702,28 @@
         <v>0.0572</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.590608680085035</v>
+        <v>-0.5719169961386154</v>
       </c>
       <c r="J27" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K27" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L27" t="n">
-        <v>0.111411871793147</v>
+        <v>0.1061909899143875</v>
       </c>
       <c r="M27" t="n">
-        <v>9.760703691765318</v>
+        <v>9.773682776860218</v>
       </c>
       <c r="N27" t="n">
-        <v>132.5360509376522</v>
+        <v>132.407711267456</v>
       </c>
       <c r="O27" t="n">
-        <v>11.5124302793829</v>
+        <v>11.50685496855922</v>
       </c>
       <c r="P27" t="n">
-        <v>391.6008182113925</v>
+        <v>391.3841012706001</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -32538,28 +32780,28 @@
         <v>0.0688</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5651796373842379</v>
+        <v>-0.5530086514568034</v>
       </c>
       <c r="J28" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K28" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1020665863879328</v>
+        <v>0.09944606168191839</v>
       </c>
       <c r="M28" t="n">
-        <v>10.10827817264624</v>
+        <v>10.08768769454422</v>
       </c>
       <c r="N28" t="n">
-        <v>133.8748184511448</v>
+        <v>133.1914067895408</v>
       </c>
       <c r="O28" t="n">
-        <v>11.57042862002721</v>
+        <v>11.54085814788228</v>
       </c>
       <c r="P28" t="n">
-        <v>382.5946996804051</v>
+        <v>382.4535853744901</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -32616,28 +32858,28 @@
         <v>0.0863</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7746297012350387</v>
+        <v>-0.7553569457455143</v>
       </c>
       <c r="J29" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K29" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2098053827921186</v>
+        <v>0.2029072158674409</v>
       </c>
       <c r="M29" t="n">
-        <v>8.711691987575502</v>
+        <v>8.731617543551236</v>
       </c>
       <c r="N29" t="n">
-        <v>107.664138541025</v>
+        <v>107.7968458265337</v>
       </c>
       <c r="O29" t="n">
-        <v>10.37613312082228</v>
+        <v>10.38252598487158</v>
       </c>
       <c r="P29" t="n">
-        <v>379.3536572087008</v>
+        <v>379.1302028979873</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -32694,28 +32936,28 @@
         <v>0.0877</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7760445042586255</v>
+        <v>-0.7547509735689231</v>
       </c>
       <c r="J30" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K30" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2304061350240991</v>
+        <v>0.2215161994704429</v>
       </c>
       <c r="M30" t="n">
-        <v>8.309538009286548</v>
+        <v>8.348953992020956</v>
       </c>
       <c r="N30" t="n">
-        <v>95.83102930283125</v>
+        <v>96.28123792342565</v>
       </c>
       <c r="O30" t="n">
-        <v>9.789332423757569</v>
+        <v>9.812300338015834</v>
       </c>
       <c r="P30" t="n">
-        <v>381.5414802884038</v>
+        <v>381.2945966048503</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -32772,28 +33014,28 @@
         <v>0.1087</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6839189462935739</v>
+        <v>-0.6687114891837762</v>
       </c>
       <c r="J31" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K31" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1926356348509101</v>
+        <v>0.1873916218832788</v>
       </c>
       <c r="M31" t="n">
-        <v>8.267810009140829</v>
+        <v>8.273782199469613</v>
       </c>
       <c r="N31" t="n">
-        <v>93.39154448130326</v>
+        <v>93.2607511428923</v>
       </c>
       <c r="O31" t="n">
-        <v>9.66393007431776</v>
+        <v>9.657160614947454</v>
       </c>
       <c r="P31" t="n">
-        <v>379.9714271879137</v>
+        <v>379.7951070974464</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -32850,28 +33092,28 @@
         <v>0.1004</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4386785130588333</v>
+        <v>-0.4299102218112624</v>
       </c>
       <c r="J32" t="n">
+        <v>248</v>
+      </c>
+      <c r="K32" t="n">
         <v>246</v>
       </c>
-      <c r="K32" t="n">
-        <v>244</v>
-      </c>
       <c r="L32" t="n">
-        <v>0.08768159300251832</v>
+        <v>0.085712017859357</v>
       </c>
       <c r="M32" t="n">
-        <v>8.328706792148054</v>
+        <v>8.294846781151548</v>
       </c>
       <c r="N32" t="n">
-        <v>94.45834086017291</v>
+        <v>93.89552278714405</v>
       </c>
       <c r="O32" t="n">
-        <v>9.718968096468519</v>
+        <v>9.689970216009131</v>
       </c>
       <c r="P32" t="n">
-        <v>387.4179815300898</v>
+        <v>387.3156720639828</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -32928,28 +33170,28 @@
         <v>0.1039</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3741531702142162</v>
+        <v>-0.3716350204137306</v>
       </c>
       <c r="J33" t="n">
+        <v>248</v>
+      </c>
+      <c r="K33" t="n">
         <v>246</v>
       </c>
-      <c r="K33" t="n">
-        <v>244</v>
-      </c>
       <c r="L33" t="n">
-        <v>0.07835660324006055</v>
+        <v>0.07864355793060118</v>
       </c>
       <c r="M33" t="n">
-        <v>7.291982381293765</v>
+        <v>7.244513299482332</v>
       </c>
       <c r="N33" t="n">
-        <v>77.67759223399653</v>
+        <v>77.06298692650991</v>
       </c>
       <c r="O33" t="n">
-        <v>8.813489220166808</v>
+        <v>8.778552666955408</v>
       </c>
       <c r="P33" t="n">
-        <v>396.2964670929476</v>
+        <v>396.2670846377452</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -33006,28 +33248,28 @@
         <v>0.0945</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.529355445217121</v>
+        <v>-0.529479849171883</v>
       </c>
       <c r="J34" t="n">
+        <v>248</v>
+      </c>
+      <c r="K34" t="n">
         <v>246</v>
       </c>
-      <c r="K34" t="n">
-        <v>244</v>
-      </c>
       <c r="L34" t="n">
-        <v>0.1519040738058871</v>
+        <v>0.1542586689406751</v>
       </c>
       <c r="M34" t="n">
-        <v>7.149394489558995</v>
+        <v>7.091780002485885</v>
       </c>
       <c r="N34" t="n">
-        <v>73.80400123194693</v>
+        <v>73.20401448467322</v>
       </c>
       <c r="O34" t="n">
-        <v>8.590925516610357</v>
+        <v>8.555934460050125</v>
       </c>
       <c r="P34" t="n">
-        <v>384.2832226946836</v>
+        <v>384.2846734270821</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -33065,7 +33307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI247"/>
+  <dimension ref="A1:AI249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76655,6 +76897,360 @@
         </is>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-36.233526220436644,175.47728857722777</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>-36.234250283855935,175.47732773627985</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>-36.23497594866262,175.4772474656071</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-36.235700232239665,175.47726927740453</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-36.23642782027694,175.47719873448838</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-36.237151167588536,175.47729106380865</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-36.23786805624349,175.47743475273398</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-36.23858700399031,175.47754527211566</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-36.23930255028113,175.47769102363344</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>-36.24001312325775,175.47785061568402</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>-36.24071480782276,175.47802325010474</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>-36.241427782366685,175.47816851158842</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>-36.24212743514308,175.47840207057058</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>-36.242835382676944,175.47859393705298</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>-36.243544442157244,175.47878018666367</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>-36.244247129498895,175.47899840846688</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>-36.24495368152678,175.47919718771874</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>-36.24567513105357,175.47932111129384</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>-36.24635840041367,175.47963676503713</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>-36.24703448520209,175.47993312738325</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>-36.24769152035529,175.48020446314294</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>-36.24832058227122,175.48060715384358</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>-36.248955702556835,175.4810263290842</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>-36.24952159518219,175.4815277282829</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>-36.250115126928904,175.48199028058806</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>-36.250749986103976,175.48243935133243</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>-36.25139968253663,175.4828643430592</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>-36.25200736386399,175.48335490374657</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>-36.252548975470354,175.48392899652134</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>-36.25305184692206,175.48456169306314</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>-36.25346713975319,175.4852862688979</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>-36.25379086595867,175.48598057759904</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>-36.25408870239918,175.4867630662391</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-36.233526323747036,175.4772809044635</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>-36.23425068214008,175.4772981569452</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>-36.234976212182026,175.47722789413606</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-36.23570045384326,175.477252819425</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-36.23642762104467,175.4772046239607</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-36.23715080914777,175.47729582575636</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-36.23786915234,175.47742337715516</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-36.23858837678424,175.4775310249036</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-36.239303422920976,175.4776819671858</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-36.240014588072725,175.47783862787549</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-36.240714524662394,175.47802488145118</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>-36.24143386841069,175.47813794438696</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>-36.242136639548995,175.4783558413426</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>-36.24284684524268,175.4785363660489</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>-36.24355947476354,175.47870468482722</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>-36.24425697926744,175.4789489376101</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>-36.244954068638506,175.479195243433</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>-36.24567409875183,175.479326296102</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>-36.24637053008076,175.47957584305152</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>-36.24704586006118,175.4798855460815</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>-36.24770716496997,175.48015912901676</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>-36.24833032877423,175.48058357229024</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>-36.248955702556835,175.4810263290842</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>-36.24952159518219,175.4815277282829</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>-36.250115126928904,175.48199028058806</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>-36.250749986103976,175.48243935133243</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>-36.25139968253663,175.4828643430592</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>-36.25200736386399,175.48335490374657</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>-36.252548975470354,175.48392899652134</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>-36.25305184692206,175.48456169306314</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>-36.25346713975319,175.4852862688979</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>-36.25379086595867,175.48598057759904</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>-36.25408870239918,175.4867630662391</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0120/nzd0120.xlsx
+++ b/data/nzd0120/nzd0120.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI249"/>
+  <dimension ref="A1:AI252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28067,6 +28067,339 @@
       <c r="AI249" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>359.61</v>
+      </c>
+      <c r="C250" t="n">
+        <v>361.16</v>
+      </c>
+      <c r="D250" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="E250" t="n">
+        <v>357.08</v>
+      </c>
+      <c r="F250" t="n">
+        <v>352.76</v>
+      </c>
+      <c r="G250" t="n">
+        <v>356.93</v>
+      </c>
+      <c r="H250" t="n">
+        <v>360.21</v>
+      </c>
+      <c r="I250" t="n">
+        <v>361.68</v>
+      </c>
+      <c r="J250" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="K250" t="n">
+        <v>373.05</v>
+      </c>
+      <c r="L250" t="n">
+        <v>376.83</v>
+      </c>
+      <c r="M250" t="n">
+        <v>368.89</v>
+      </c>
+      <c r="N250" t="n">
+        <v>370.53</v>
+      </c>
+      <c r="O250" t="n">
+        <v>368.71</v>
+      </c>
+      <c r="P250" t="n">
+        <v>359.46</v>
+      </c>
+      <c r="Q250" t="n">
+        <v>359.17</v>
+      </c>
+      <c r="R250" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="S250" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="T250" t="n">
+        <v>372.28</v>
+      </c>
+      <c r="U250" t="n">
+        <v>382.71</v>
+      </c>
+      <c r="V250" t="n">
+        <v>383.22</v>
+      </c>
+      <c r="W250" t="n">
+        <v>386.9</v>
+      </c>
+      <c r="X250" t="n">
+        <v>391.97</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>402.1</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>396.33</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>386.9</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>374.75</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>370.12</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>373.46</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>370.76</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>380.89</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>387.22</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>370.19</v>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>359.61</v>
+      </c>
+      <c r="C251" t="n">
+        <v>361.16</v>
+      </c>
+      <c r="D251" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="E251" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="F251" t="n">
+        <v>351.27</v>
+      </c>
+      <c r="G251" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="H251" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="I251" t="n">
+        <v>359.74</v>
+      </c>
+      <c r="J251" t="n">
+        <v>362.53</v>
+      </c>
+      <c r="K251" t="n">
+        <v>369.48</v>
+      </c>
+      <c r="L251" t="n">
+        <v>371.81</v>
+      </c>
+      <c r="M251" t="n">
+        <v>365.61</v>
+      </c>
+      <c r="N251" t="n">
+        <v>365.01</v>
+      </c>
+      <c r="O251" t="n">
+        <v>363.87</v>
+      </c>
+      <c r="P251" t="n">
+        <v>357.09</v>
+      </c>
+      <c r="Q251" t="n">
+        <v>357.21</v>
+      </c>
+      <c r="R251" t="n">
+        <v>369.68</v>
+      </c>
+      <c r="S251" t="n">
+        <v>362.26</v>
+      </c>
+      <c r="T251" t="n">
+        <v>368.97</v>
+      </c>
+      <c r="U251" t="n">
+        <v>379.46</v>
+      </c>
+      <c r="V251" t="n">
+        <v>380.32</v>
+      </c>
+      <c r="W251" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="X251" t="n">
+        <v>388.56</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>397.07</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>393.86</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>385.88</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>376.03</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>370.69</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>380.92</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>387.39</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>369.49</v>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>359.61</v>
+      </c>
+      <c r="C252" t="n">
+        <v>361.16</v>
+      </c>
+      <c r="D252" t="n">
+        <v>354.84</v>
+      </c>
+      <c r="E252" t="n">
+        <v>354.97</v>
+      </c>
+      <c r="F252" t="n">
+        <v>351.27</v>
+      </c>
+      <c r="G252" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="H252" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="I252" t="n">
+        <v>359.74</v>
+      </c>
+      <c r="J252" t="n">
+        <v>362.53</v>
+      </c>
+      <c r="K252" t="n">
+        <v>369.48</v>
+      </c>
+      <c r="L252" t="n">
+        <v>367.19</v>
+      </c>
+      <c r="M252" t="n">
+        <v>360.73</v>
+      </c>
+      <c r="N252" t="n">
+        <v>360.66</v>
+      </c>
+      <c r="O252" t="n">
+        <v>358.13</v>
+      </c>
+      <c r="P252" t="n">
+        <v>353.13</v>
+      </c>
+      <c r="Q252" t="n">
+        <v>355.19</v>
+      </c>
+      <c r="R252" t="n">
+        <v>366.27</v>
+      </c>
+      <c r="S252" t="n">
+        <v>358.16</v>
+      </c>
+      <c r="T252" t="n">
+        <v>364.62</v>
+      </c>
+      <c r="U252" t="n">
+        <v>375.83</v>
+      </c>
+      <c r="V252" t="n">
+        <v>376.68</v>
+      </c>
+      <c r="W252" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="X252" t="n">
+        <v>384.93</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>392.8</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>389.54</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>382.47</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>365.98</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>370.08</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>368.28</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>377.44</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28081,7 +28414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B250"/>
+  <dimension ref="A1:B253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30584,6 +30917,36 @@
       </c>
       <c r="B250" t="n">
         <v>-0.59</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -30752,28 +31115,28 @@
         <v>0.0663</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1312751063596569</v>
+        <v>-0.136894200954489</v>
       </c>
       <c r="J2" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K2" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002768328975716994</v>
+        <v>0.003089648996819183</v>
       </c>
       <c r="M2" t="n">
-        <v>14.85718293667566</v>
+        <v>14.6946070308902</v>
       </c>
       <c r="N2" t="n">
-        <v>301.7080983622513</v>
+        <v>298.0565213756427</v>
       </c>
       <c r="O2" t="n">
-        <v>17.3697466407041</v>
+        <v>17.26431352170259</v>
       </c>
       <c r="P2" t="n">
-        <v>365.3216572733813</v>
+        <v>365.3872003986892</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -30830,28 +31193,28 @@
         <v>0.0613</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2946708012897212</v>
+        <v>-0.2913774451323519</v>
       </c>
       <c r="J3" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K3" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01409342030369953</v>
+        <v>0.01414489075587988</v>
       </c>
       <c r="M3" t="n">
-        <v>14.05357270861096</v>
+        <v>13.9039057792252</v>
       </c>
       <c r="N3" t="n">
-        <v>293.7180352265968</v>
+        <v>290.1992665853815</v>
       </c>
       <c r="O3" t="n">
-        <v>17.13820396735308</v>
+        <v>17.03523602963521</v>
       </c>
       <c r="P3" t="n">
-        <v>367.712333102666</v>
+        <v>367.6738879685357</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30908,28 +31271,28 @@
         <v>0.07679999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3069365514573178</v>
+        <v>-0.3083398569718405</v>
       </c>
       <c r="J4" t="n">
+        <v>251</v>
+      </c>
+      <c r="K4" t="n">
         <v>248</v>
       </c>
-      <c r="K4" t="n">
-        <v>245</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.0150552883015852</v>
+        <v>0.01559222430270346</v>
       </c>
       <c r="M4" t="n">
-        <v>14.31715462918932</v>
+        <v>14.15023131748706</v>
       </c>
       <c r="N4" t="n">
-        <v>298.1294376533864</v>
+        <v>294.5266356814726</v>
       </c>
       <c r="O4" t="n">
-        <v>17.26642515558407</v>
+        <v>17.16177833680043</v>
       </c>
       <c r="P4" t="n">
-        <v>363.5843765385849</v>
+        <v>363.6007346155364</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30986,28 +31349,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2564767591734949</v>
+        <v>-0.2505243400666927</v>
       </c>
       <c r="J5" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K5" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01164966251045696</v>
+        <v>0.01141325510086899</v>
       </c>
       <c r="M5" t="n">
-        <v>13.2820220532156</v>
+        <v>13.1528337491493</v>
       </c>
       <c r="N5" t="n">
-        <v>270.0846396832442</v>
+        <v>266.9073169044268</v>
       </c>
       <c r="O5" t="n">
-        <v>16.43425202688714</v>
+        <v>16.33729833553966</v>
       </c>
       <c r="P5" t="n">
-        <v>360.1513971510988</v>
+        <v>360.0821462837505</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31064,28 +31427,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2761543756578764</v>
+        <v>-0.2858910116548897</v>
       </c>
       <c r="J6" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K6" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01741130817684733</v>
+        <v>0.01910613981665321</v>
       </c>
       <c r="M6" t="n">
-        <v>11.66183866899529</v>
+        <v>11.56026824668673</v>
       </c>
       <c r="N6" t="n">
-        <v>210.0946566112819</v>
+        <v>207.7661342288362</v>
       </c>
       <c r="O6" t="n">
-        <v>14.49464234161305</v>
+        <v>14.41409498473061</v>
       </c>
       <c r="P6" t="n">
-        <v>363.0527583810164</v>
+        <v>363.1655708796711</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31142,28 +31505,28 @@
         <v>0.0993</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3271904352192705</v>
+        <v>-0.330818195822592</v>
       </c>
       <c r="J7" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K7" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02192150355132427</v>
+        <v>0.02297744534757284</v>
       </c>
       <c r="M7" t="n">
-        <v>12.55202607523866</v>
+        <v>12.41792179099235</v>
       </c>
       <c r="N7" t="n">
-        <v>233.1714434891171</v>
+        <v>230.4126490942242</v>
       </c>
       <c r="O7" t="n">
-        <v>15.26995230801711</v>
+        <v>15.17934942921548</v>
       </c>
       <c r="P7" t="n">
-        <v>366.3377105608581</v>
+        <v>366.3797500625852</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31220,28 +31583,28 @@
         <v>0.0776</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4121096896178313</v>
+        <v>-0.4102223700606099</v>
       </c>
       <c r="J8" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K8" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03507282001265966</v>
+        <v>0.03565192379657633</v>
       </c>
       <c r="M8" t="n">
-        <v>12.32552234734423</v>
+        <v>12.18618475564933</v>
       </c>
       <c r="N8" t="n">
-        <v>228.097378921032</v>
+        <v>225.3794005466072</v>
       </c>
       <c r="O8" t="n">
-        <v>15.10289306460957</v>
+        <v>15.01264135808909</v>
       </c>
       <c r="P8" t="n">
-        <v>369.9151858092152</v>
+        <v>369.8933305072208</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31298,28 +31661,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4436404396187437</v>
+        <v>-0.4568277257134162</v>
       </c>
       <c r="J9" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K9" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04335969956487695</v>
+        <v>0.04694425901634036</v>
       </c>
       <c r="M9" t="n">
-        <v>11.90034889587331</v>
+        <v>11.82602449438315</v>
       </c>
       <c r="N9" t="n">
-        <v>211.9802753254733</v>
+        <v>209.7806435835511</v>
       </c>
       <c r="O9" t="n">
-        <v>14.55954241470086</v>
+        <v>14.48380625331446</v>
       </c>
       <c r="P9" t="n">
-        <v>377.5374637197315</v>
+        <v>377.690255787763</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31376,28 +31739,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5367918479599988</v>
+        <v>-0.5533809289532734</v>
       </c>
       <c r="J10" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K10" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06262968198735719</v>
+        <v>0.06776780972417307</v>
       </c>
       <c r="M10" t="n">
-        <v>11.77086430992744</v>
+        <v>11.71752175503099</v>
       </c>
       <c r="N10" t="n">
-        <v>210.5298127682835</v>
+        <v>208.5805045664725</v>
       </c>
       <c r="O10" t="n">
-        <v>14.50964550801581</v>
+        <v>14.44231645431135</v>
       </c>
       <c r="P10" t="n">
-        <v>385.0446649587525</v>
+        <v>385.2368951132641</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31454,28 +31817,28 @@
         <v>0.0703</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7410204820560077</v>
+        <v>-0.7451571604672268</v>
       </c>
       <c r="J11" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K11" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L11" t="n">
-        <v>0.08781311104258505</v>
+        <v>0.09083314431570122</v>
       </c>
       <c r="M11" t="n">
-        <v>13.05740363631243</v>
+        <v>12.92763603646756</v>
       </c>
       <c r="N11" t="n">
-        <v>279.5184953212283</v>
+        <v>276.2295523663249</v>
       </c>
       <c r="O11" t="n">
-        <v>16.71880663567913</v>
+        <v>16.62015500428095</v>
       </c>
       <c r="P11" t="n">
-        <v>392.1039596748012</v>
+        <v>392.1518323398493</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31532,28 +31895,28 @@
         <v>0.0771</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9095053275743888</v>
+        <v>-0.9062069509380556</v>
       </c>
       <c r="J12" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K12" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1291390309410927</v>
+        <v>0.1312008164622491</v>
       </c>
       <c r="M12" t="n">
-        <v>12.57205537433814</v>
+        <v>12.46399348221921</v>
       </c>
       <c r="N12" t="n">
-        <v>273.3552764390033</v>
+        <v>270.2792961863347</v>
       </c>
       <c r="O12" t="n">
-        <v>16.53345930043085</v>
+        <v>16.44017324076406</v>
       </c>
       <c r="P12" t="n">
-        <v>394.8759333479719</v>
+        <v>394.8379156216395</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31610,28 +31973,28 @@
         <v>0.0861</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.745646230254745</v>
+        <v>-0.7552512116564074</v>
       </c>
       <c r="J13" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K13" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1013201917717891</v>
+        <v>0.1060170064018606</v>
       </c>
       <c r="M13" t="n">
-        <v>12.53038931228133</v>
+        <v>12.41872584205253</v>
       </c>
       <c r="N13" t="n">
-        <v>241.6575105177559</v>
+        <v>239.0626429170633</v>
       </c>
       <c r="O13" t="n">
-        <v>15.54533725969803</v>
+        <v>15.46165071772944</v>
       </c>
       <c r="P13" t="n">
-        <v>388.8303879879056</v>
+        <v>388.9415570545444</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31688,28 +32051,28 @@
         <v>0.1244</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8507926568769789</v>
+        <v>-0.8465232269572482</v>
       </c>
       <c r="J14" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K14" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1285014100764571</v>
+        <v>0.1302146027557656</v>
       </c>
       <c r="M14" t="n">
-        <v>12.68271006963552</v>
+        <v>12.5727417587132</v>
       </c>
       <c r="N14" t="n">
-        <v>240.5647134869037</v>
+        <v>237.9059556128149</v>
       </c>
       <c r="O14" t="n">
-        <v>15.51014872549273</v>
+        <v>15.42420032328467</v>
       </c>
       <c r="P14" t="n">
-        <v>386.3756261268562</v>
+        <v>386.3263819279528</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31766,28 +32129,28 @@
         <v>0.1041</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6900037946122598</v>
+        <v>-0.6852758650482698</v>
       </c>
       <c r="J15" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K15" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1424997105934247</v>
+        <v>0.1437918186111119</v>
       </c>
       <c r="M15" t="n">
-        <v>10.08746779435898</v>
+        <v>10.01994238742383</v>
       </c>
       <c r="N15" t="n">
-        <v>139.8601665258326</v>
+        <v>138.4524871074186</v>
       </c>
       <c r="O15" t="n">
-        <v>11.82624904717606</v>
+        <v>11.76658349341127</v>
       </c>
       <c r="P15" t="n">
-        <v>380.0669644924277</v>
+        <v>380.0123282757218</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31844,28 +32207,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5852847886978173</v>
+        <v>-0.5944109635576993</v>
       </c>
       <c r="J16" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K16" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1106944501843604</v>
+        <v>0.1162676274963858</v>
       </c>
       <c r="M16" t="n">
-        <v>9.840441506629348</v>
+        <v>9.770251944028571</v>
       </c>
       <c r="N16" t="n">
-        <v>134.8606636893585</v>
+        <v>133.4783134917669</v>
       </c>
       <c r="O16" t="n">
-        <v>11.61295241053534</v>
+        <v>11.55328150318198</v>
       </c>
       <c r="P16" t="n">
-        <v>375.844206754321</v>
+        <v>375.9498160757774</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31922,28 +32285,28 @@
         <v>0.2</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5650168398035013</v>
+        <v>-0.567053229371691</v>
       </c>
       <c r="J17" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K17" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08586500499703353</v>
+        <v>0.08850333769683338</v>
       </c>
       <c r="M17" t="n">
-        <v>10.78036944482125</v>
+        <v>10.67052167852762</v>
       </c>
       <c r="N17" t="n">
-        <v>165.9157859929904</v>
+        <v>163.9712778556858</v>
       </c>
       <c r="O17" t="n">
-        <v>12.88083017483696</v>
+        <v>12.80512701443003</v>
       </c>
       <c r="P17" t="n">
-        <v>373.083026160236</v>
+        <v>373.1066672568013</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32000,28 +32363,28 @@
         <v>0.2</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5734747028874323</v>
+        <v>-0.5343892098122099</v>
       </c>
       <c r="J18" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K18" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L18" t="n">
-        <v>0.08252878902102567</v>
+        <v>0.07308829639692194</v>
       </c>
       <c r="M18" t="n">
-        <v>11.07865551132486</v>
+        <v>11.12474264392873</v>
       </c>
       <c r="N18" t="n">
-        <v>178.4786584744382</v>
+        <v>179.3207634971903</v>
       </c>
       <c r="O18" t="n">
-        <v>13.35959050549223</v>
+        <v>13.39107028945746</v>
       </c>
       <c r="P18" t="n">
-        <v>369.5748310861912</v>
+        <v>369.1221359655529</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32078,28 +32441,28 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5709253572817011</v>
+        <v>-0.5523184506085269</v>
       </c>
       <c r="J19" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K19" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L19" t="n">
-        <v>0.100792819396832</v>
+        <v>0.09670254808480117</v>
       </c>
       <c r="M19" t="n">
-        <v>10.42294312250323</v>
+        <v>10.38410090022192</v>
       </c>
       <c r="N19" t="n">
-        <v>141.9579199736391</v>
+        <v>141.0901391843215</v>
       </c>
       <c r="O19" t="n">
-        <v>11.91460951830311</v>
+        <v>11.87813702498509</v>
       </c>
       <c r="P19" t="n">
-        <v>370.4436476913031</v>
+        <v>370.2282116254141</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32156,28 +32519,28 @@
         <v>0.0849</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3529741643035026</v>
+        <v>-0.3331293450198143</v>
       </c>
       <c r="J20" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K20" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03967334835602698</v>
+        <v>0.03619629032731231</v>
       </c>
       <c r="M20" t="n">
-        <v>10.24798567247942</v>
+        <v>10.21870076507862</v>
       </c>
       <c r="N20" t="n">
-        <v>147.7854324696974</v>
+        <v>146.8674137320405</v>
       </c>
       <c r="O20" t="n">
-        <v>12.15670319082018</v>
+        <v>12.11888665398107</v>
       </c>
       <c r="P20" t="n">
-        <v>370.0490393011399</v>
+        <v>369.8196709202037</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32234,28 +32597,28 @@
         <v>0.1177</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.523088346297637</v>
+        <v>-0.4832400672396913</v>
       </c>
       <c r="J21" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K21" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06599758017237567</v>
+        <v>0.05741154097351886</v>
       </c>
       <c r="M21" t="n">
-        <v>11.5452709967642</v>
+        <v>11.59912098841335</v>
       </c>
       <c r="N21" t="n">
-        <v>189.0344109200172</v>
+        <v>189.8337723390457</v>
       </c>
       <c r="O21" t="n">
-        <v>13.74897854096868</v>
+        <v>13.77801772168427</v>
       </c>
       <c r="P21" t="n">
-        <v>377.2383984107556</v>
+        <v>376.7768564171117</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32312,28 +32675,28 @@
         <v>0.07729999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6820196269420797</v>
+        <v>-0.6422830659736524</v>
       </c>
       <c r="J22" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K22" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1083873551199093</v>
+        <v>0.09821187219397209</v>
       </c>
       <c r="M22" t="n">
-        <v>11.58670992514755</v>
+        <v>11.63705703345728</v>
       </c>
       <c r="N22" t="n">
-        <v>184.3864888012958</v>
+        <v>185.1526234586688</v>
       </c>
       <c r="O22" t="n">
-        <v>13.57889865936468</v>
+        <v>13.60707990197268</v>
       </c>
       <c r="P22" t="n">
-        <v>382.4406515301198</v>
+        <v>381.9767309378328</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -32390,28 +32753,28 @@
         <v>0.0822</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8315123537854106</v>
+        <v>-0.7745000837641023</v>
       </c>
       <c r="J23" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K23" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1393906080444529</v>
+        <v>0.1228455200329656</v>
       </c>
       <c r="M23" t="n">
-        <v>12.12684907923363</v>
+        <v>12.23557950239639</v>
       </c>
       <c r="N23" t="n">
-        <v>208.3918693219768</v>
+        <v>212.07251782513</v>
       </c>
       <c r="O23" t="n">
-        <v>14.43578433345334</v>
+        <v>14.56270983797761</v>
       </c>
       <c r="P23" t="n">
-        <v>383.0267315959823</v>
+        <v>382.3663557295415</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -32468,28 +32831,28 @@
         <v>0.1105</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.7871546833880105</v>
+        <v>-0.7352339852328621</v>
       </c>
       <c r="J24" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K24" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1417549718793611</v>
+        <v>0.1257549701623515</v>
       </c>
       <c r="M24" t="n">
-        <v>11.28799187152317</v>
+        <v>11.36136152753396</v>
       </c>
       <c r="N24" t="n">
-        <v>183.1318798004872</v>
+        <v>186.0732110496865</v>
       </c>
       <c r="O24" t="n">
-        <v>13.53262279827851</v>
+        <v>13.64086548022839</v>
       </c>
       <c r="P24" t="n">
-        <v>388.5777922687729</v>
+        <v>387.97639660185</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -32546,28 +32909,28 @@
         <v>0.0989</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.764179509930236</v>
+        <v>-0.7127683614311594</v>
       </c>
       <c r="J25" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K25" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1623288234131177</v>
+        <v>0.1432407359781225</v>
       </c>
       <c r="M25" t="n">
-        <v>9.994071898206808</v>
+        <v>10.06878205539754</v>
       </c>
       <c r="N25" t="n">
-        <v>147.1090864345057</v>
+        <v>150.4574804163364</v>
       </c>
       <c r="O25" t="n">
-        <v>12.12885346743482</v>
+        <v>12.26611105511182</v>
       </c>
       <c r="P25" t="n">
-        <v>396.9996581086074</v>
+        <v>396.4041928721016</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -32624,28 +32987,28 @@
         <v>0.06560000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.619409358320572</v>
+        <v>-0.5822244312978293</v>
       </c>
       <c r="J26" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K26" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1305982517659046</v>
+        <v>0.1176915599405629</v>
       </c>
       <c r="M26" t="n">
-        <v>9.435862059060746</v>
+        <v>9.484320467682799</v>
       </c>
       <c r="N26" t="n">
-        <v>122.8369104227538</v>
+        <v>123.9823648446974</v>
       </c>
       <c r="O26" t="n">
-        <v>11.0831814215393</v>
+        <v>11.1347368556557</v>
       </c>
       <c r="P26" t="n">
-        <v>394.9813633300875</v>
+        <v>394.5468401645192</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -32702,28 +33065,28 @@
         <v>0.0572</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5719169961386154</v>
+        <v>-0.5493914878128258</v>
       </c>
       <c r="J27" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K27" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1061909899143875</v>
+        <v>0.1005054202404304</v>
       </c>
       <c r="M27" t="n">
-        <v>9.773682776860218</v>
+        <v>9.763807616663643</v>
       </c>
       <c r="N27" t="n">
-        <v>132.407711267456</v>
+        <v>131.7883043205757</v>
       </c>
       <c r="O27" t="n">
-        <v>11.50685496855922</v>
+        <v>11.47990872440089</v>
       </c>
       <c r="P27" t="n">
-        <v>391.3841012706001</v>
+        <v>391.1208859870924</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -32780,28 +33143,28 @@
         <v>0.0688</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.5530086514568034</v>
+        <v>-0.5360890544806355</v>
       </c>
       <c r="J28" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K28" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L28" t="n">
-        <v>0.09944606168191839</v>
+        <v>0.09592729174198944</v>
       </c>
       <c r="M28" t="n">
-        <v>10.08768769454422</v>
+        <v>10.04924923091063</v>
       </c>
       <c r="N28" t="n">
-        <v>133.1914067895408</v>
+        <v>132.1414313516236</v>
       </c>
       <c r="O28" t="n">
-        <v>11.54085814788228</v>
+        <v>11.49527865480535</v>
       </c>
       <c r="P28" t="n">
-        <v>382.4535853744901</v>
+        <v>382.2558668664977</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -32858,28 +33221,28 @@
         <v>0.0863</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7553569457455143</v>
+        <v>-0.7318758482641829</v>
       </c>
       <c r="J29" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K29" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2029072158674409</v>
+        <v>0.1954874472992669</v>
       </c>
       <c r="M29" t="n">
-        <v>8.731617543551236</v>
+        <v>8.735914001629324</v>
       </c>
       <c r="N29" t="n">
-        <v>107.7968458265337</v>
+        <v>107.5456209453288</v>
       </c>
       <c r="O29" t="n">
-        <v>10.38252598487158</v>
+        <v>10.37042048064247</v>
       </c>
       <c r="P29" t="n">
-        <v>379.1302028979873</v>
+        <v>378.855813707196</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -32936,28 +33299,28 @@
         <v>0.0877</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7547509735689231</v>
+        <v>-0.7271875431661592</v>
       </c>
       <c r="J30" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K30" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2215161994704429</v>
+        <v>0.210881729395049</v>
       </c>
       <c r="M30" t="n">
-        <v>8.348953992020956</v>
+        <v>8.383159178008572</v>
       </c>
       <c r="N30" t="n">
-        <v>96.28123792342565</v>
+        <v>96.53836885115487</v>
       </c>
       <c r="O30" t="n">
-        <v>9.812300338015834</v>
+        <v>9.825394081213988</v>
       </c>
       <c r="P30" t="n">
-        <v>381.2945966048503</v>
+        <v>380.9724845352633</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -33014,28 +33377,28 @@
         <v>0.1087</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6687114891837762</v>
+        <v>-0.6486936515366237</v>
       </c>
       <c r="J31" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K31" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L31" t="n">
-        <v>0.1873916218832788</v>
+        <v>0.1810083199731721</v>
       </c>
       <c r="M31" t="n">
-        <v>8.273782199469613</v>
+        <v>8.267713817234307</v>
       </c>
       <c r="N31" t="n">
-        <v>93.2607511428923</v>
+        <v>92.8889809728291</v>
       </c>
       <c r="O31" t="n">
-        <v>9.657160614947454</v>
+        <v>9.637892973717289</v>
       </c>
       <c r="P31" t="n">
-        <v>379.7951070974464</v>
+        <v>379.5611759060732</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -33092,28 +33455,28 @@
         <v>0.1004</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4299102218112624</v>
+        <v>-0.4200031868902875</v>
       </c>
       <c r="J32" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K32" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L32" t="n">
-        <v>0.085712017859357</v>
+        <v>0.08397290478696695</v>
       </c>
       <c r="M32" t="n">
-        <v>8.294846781151548</v>
+        <v>8.232017544979538</v>
       </c>
       <c r="N32" t="n">
-        <v>93.89552278714405</v>
+        <v>92.97309369151223</v>
       </c>
       <c r="O32" t="n">
-        <v>9.689970216009131</v>
+        <v>9.642255632968473</v>
       </c>
       <c r="P32" t="n">
-        <v>387.3156720639828</v>
+        <v>387.1991979483561</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -33170,28 +33533,28 @@
         <v>0.1039</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3716350204137306</v>
+        <v>-0.3710167558507868</v>
       </c>
       <c r="J33" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K33" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L33" t="n">
-        <v>0.07864355793060118</v>
+        <v>0.0803250206900642</v>
       </c>
       <c r="M33" t="n">
-        <v>7.244513299482332</v>
+        <v>7.169429534337747</v>
       </c>
       <c r="N33" t="n">
-        <v>77.06298692650991</v>
+        <v>76.14713012225359</v>
       </c>
       <c r="O33" t="n">
-        <v>8.778552666955408</v>
+        <v>8.726232298206002</v>
       </c>
       <c r="P33" t="n">
-        <v>396.2670846377452</v>
+        <v>396.2598423717052</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -33248,28 +33611,28 @@
         <v>0.0945</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.529479849171883</v>
+        <v>-0.5320928678909945</v>
       </c>
       <c r="J34" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K34" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1542586689406751</v>
+        <v>0.1590108579748654</v>
       </c>
       <c r="M34" t="n">
-        <v>7.091780002485885</v>
+        <v>7.017152803193668</v>
       </c>
       <c r="N34" t="n">
-        <v>73.20401448467322</v>
+        <v>72.34715389204142</v>
       </c>
       <c r="O34" t="n">
-        <v>8.555934460050125</v>
+        <v>8.505713014911885</v>
       </c>
       <c r="P34" t="n">
-        <v>384.2846734270821</v>
+        <v>384.315440357605</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -33307,7 +33670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI249"/>
+  <dimension ref="A1:AI252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77251,6 +77614,537 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>-36.233526323747036,175.4772809044635</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>-36.23425068214008,175.4772981569452</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>-36.234976212182026,175.47722789413606</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>-36.23570045384326,175.477252819425</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-36.23642762104467,175.4772046239607</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-36.23715080914777,175.47729582575636</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-36.23786915234,175.47742337715516</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-36.23858837678424,175.4775310249036</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-36.239303422920976,175.4776819671858</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-36.240014588072725,175.47783862787549</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-36.240714524662394,175.47802488145118</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>-36.24143386841069,175.47813794438696</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>-36.242136639548995,175.4783558413426</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>-36.24284684524268,175.4785363660489</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>-36.243573023424524,175.47863663593472</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>-36.24427992613966,175.47883368558323</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>-36.244954068638506,175.479195243433</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>-36.24567409875183,175.479326296102</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>-36.24637053008076,175.47957584305152</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>-36.24704586006118,175.4798855460815</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>-36.24770716496997,175.48015912901676</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>-36.24833032877423,175.48058357229024</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>-36.248955702556835,175.4810263290842</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>-36.24952159518219,175.4815277282829</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>-36.250115126928904,175.48199028058806</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>-36.250749986103976,175.48243935133243</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>-36.25139968253663,175.4828643430592</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>-36.25200736386399,175.48335490374657</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>-36.252548975470354,175.48392899652134</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>-36.25305184692206,175.48456169306314</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>-36.25346713975319,175.4852862688979</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>-36.25379610584869,175.4859778827346</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>-36.25408870239918,175.4867630662391</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>-36.233526323747036,175.4772809044635</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>-36.23425068214008,175.4772981569452</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>-36.234976212182026,175.47722789413606</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-36.235700769774205,175.4772293556835</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-36.2364281811497,175.4771880667648</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-36.237151792775464,175.47728275808572</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-36.237870003676335,175.4774145417539</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-36.238590441292914,175.47750959886255</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-36.23930825435377,175.47763182538583</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-36.24001938566951,175.47779936504935</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>-36.24072400108418,175.4779702857172</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>-36.241440922190634,175.47810251666994</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>-36.24214851062615,175.4782962185825</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>-36.242857254003084,175.47848408767285</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>-36.24357812029196,175.4786110365828</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>-36.244284141298394,175.47881251463122</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>-36.2449635958787,175.47914739239357</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>-36.245685819664885,175.47926742691726</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>-36.24637764871876,175.47954008918157</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>-36.24705414890427,175.47985087359893</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>-36.247717406356614,175.480129452039</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>-36.24833933814282,175.48056177421032</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>-36.24897015400875,175.48099285534954</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>-36.24954639925867,175.48148089982317</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>-36.25012860393243,175.4819684157025</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>-36.25075555152713,175.4824303220591</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>-36.251392698451795,175.4828756739776</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>-36.252014547467674,175.48334362265405</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>-36.25255302001859,175.4839237670573</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>-36.25305231757881,175.4845611747062</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>-36.253466926705435,175.48528647428574</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>-36.25379469191012,175.48597860992027</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>-36.25409488498917,175.48676152712326</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>-36.233526323747036,175.4772809044635</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>-36.23425068214008,175.4772981569452</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>-36.234976212182026,175.47722789413606</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-36.235700769774205,175.4772293556835</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-36.2364281811497,175.4771880667648</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-36.237151792775464,175.47728275808572</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-36.237870003676335,175.4774145417539</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-36.238590441292914,175.47750959886255</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-36.23930825435377,175.47763182538583</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-36.24001938566951,175.47779936504935</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>-36.24073272239099,175.47792004022804</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>-36.24145141681986,175.4780498071269</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>-36.24215786553059,175.4782492332414</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>-36.24286959824781,175.47842208809152</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>-36.243586636564814,175.47856826297402</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>-36.24428848548874,175.47879069558624</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>-36.24497092947521,175.4791105589663</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>-36.24569463721384,175.47922313999499</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>-36.24638700401265,175.47949310145654</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>-36.24706340689285,175.47981214709367</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>-36.24773026105258,175.48009220230375</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>-36.248359322546854,175.48051342208728</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>-36.24898553780259,175.48095722200515</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>-36.24956745558836,175.48144114681273</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>-36.25015217503892,175.48193017426493</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>-36.25077415749596,175.48240013594958</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>-36.251412013808945,175.48284433690137</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>-36.252030418216535,175.48331869930266</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>-36.25257000711887,175.48390180330236</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>-36.253068521617166,175.4845433284136</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>-36.25349164024104,175.48526264928756</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>-36.25381307311128,175.48596915650452</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>-36.25411069475492,175.48675759138322</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
